--- a/player_stats/stats_2025_2026.xlsx
+++ b/player_stats/stats_2025_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\data\private\MaLo\yearly_stats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\data\private\MaLo\matchCounter\player_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F10D7F-D3C7-437F-8EBD-56B993C12066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78304630-B8CB-4901-8CC1-5AEBF39CDA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Zusammenfassung" sheetId="1" r:id="rId1"/>
@@ -684,14 +684,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -731,7 +731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -771,7 +771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -791,7 +791,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -811,7 +811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -851,7 +851,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -911,7 +911,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -931,7 +931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -951,7 +951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -971,7 +971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -991,7 +991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1802,7 +1802,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D896"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1810,7 +1810,7 @@
     <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>51</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>59</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>23</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>40</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>36</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>40</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>33</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>27</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>54</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>42</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>59</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>42</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>58</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>49</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>26</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>40</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>36</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>55</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>27</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>42</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>58</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>15</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>49</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>13</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>40</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>36</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>59</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>26</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>55</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>23</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>29</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>49</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>13</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>36</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>59</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>27</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>42</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>58</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>15</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>26</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>51</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>23</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>29</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>27</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>42</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>58</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>15</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>49</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>13</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>26</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>51</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>36</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>33</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>23</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>34</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>29</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>49</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>13</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>51</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>36</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>59</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>27</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>8</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>58</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>34</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>29</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>25</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>23</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>15</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>27</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>58</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>34</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>29</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>49</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>13</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>51</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>11</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>36</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>59</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>26</v>
       </c>
@@ -3924,7 +3924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>40</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>33</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>23</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>15</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>49</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>13</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>26</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>36</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>59</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>34</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>27</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>15</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>8</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>58</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>51</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>29</v>
       </c>
@@ -4162,7 +4162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>23</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>49</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>13</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>51</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>11</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>40</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>59</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>33</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>27</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>8</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>58</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>34</v>
       </c>
@@ -4330,7 +4330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>26</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>36</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>55</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>23</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>29</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>27</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>8</v>
       </c>
@@ -4428,7 +4428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>58</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>34</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>29</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>49</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>13</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>51</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>11</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>40</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>36</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>55</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>33</v>
       </c>
@@ -4582,7 +4582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>23</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>15</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>49</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>13</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>51</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>11</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>40</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>36</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>27</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>8</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>58</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>34</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>29</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>26</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>55</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>33</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>15</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>49</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>26</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>51</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>11</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>36</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>33</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>27</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>8</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>58</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>34</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>15</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>13</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>40</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>55</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>29</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>27</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>8</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>58</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>34</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>15</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>49</v>
       </c>
@@ -5114,7 +5114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>26</v>
       </c>
@@ -5128,7 +5128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>51</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>11</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>36</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>33</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>13</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>55</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>59</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>23</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>29</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>49</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>13</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>26</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>51</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>11</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>27</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>8</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>58</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>34</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>29</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>15</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>40</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>36</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>59</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>23</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>8</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>58</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>34</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>29</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>15</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>49</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>13</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>26</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>51</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>11</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>27</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>40</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>32</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>23</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>59</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>8</v>
       </c>
@@ -5688,7 +5688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>34</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>29</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>15</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>49</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>26</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>51</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>11</v>
       </c>
@@ -5786,7 +5786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>36</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>55</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>13</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>32</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>23</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>58</v>
       </c>
@@ -5870,7 +5870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>27</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>23</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>8</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>34</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>15</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>49</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>13</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>26</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>36</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>55</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>59</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>51</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>33</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>55</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>59</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>58</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>34</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>15</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>49</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>13</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>26</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>51</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>11</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>36</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>32</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>33</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>55</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>59</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>27</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>29</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>15</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>49</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>40</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>26</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>51</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>11</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>36</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>23</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>49</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>13</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>26</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>51</v>
       </c>
@@ -6458,7 +6458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>11</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>36</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>27</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>8</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>58</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>34</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>29</v>
       </c>
@@ -6556,7 +6556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>55</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>59</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>33</v>
       </c>
@@ -6598,7 +6598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>42</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>23</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>15</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>49</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>13</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>26</v>
       </c>
@@ -6682,7 +6682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>11</v>
       </c>
@@ -6696,7 +6696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>36</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>59</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>27</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>8</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>58</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>34</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>29</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>32</v>
       </c>
@@ -6808,7 +6808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>55</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>23</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>15</v>
       </c>
@@ -6850,7 +6850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>55</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>59</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>27</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>8</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>29</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>49</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>13</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>26</v>
       </c>
@@ -6962,7 +6962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>51</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>11</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>36</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>32</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>37</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>20</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>58</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>15</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>49</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>13</v>
       </c>
@@ -7102,7 +7102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>51</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>11</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>36</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>55</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>59</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>27</v>
       </c>
@@ -7186,7 +7186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>58</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>34</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>29</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>26</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>32</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>23</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>32</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>27</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>8</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>34</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>15</v>
       </c>
@@ -7340,7 +7340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>49</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>13</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>40</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>51</v>
       </c>
@@ -7396,7 +7396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>11</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>36</v>
       </c>
@@ -7424,7 +7424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>48</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>33</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>52</v>
       </c>
@@ -7466,7 +7466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>23</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>49</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>13</v>
       </c>
@@ -7508,7 +7508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>26</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>11</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>36</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>32</v>
       </c>
@@ -7564,7 +7564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>57</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>27</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>40</v>
       </c>
@@ -7606,7 +7606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>8</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>15</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>33</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>44</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>23</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>58</v>
       </c>
@@ -7690,7 +7690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>48</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>27</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>8</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>34</v>
       </c>
@@ -7746,7 +7746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>29</v>
       </c>
@@ -7760,7 +7760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>15</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>49</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>13</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>26</v>
       </c>
@@ -7816,7 +7816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>51</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>36</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>57</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>32</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>37</v>
       </c>
@@ -7886,7 +7886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>33</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>23</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>49</v>
       </c>
@@ -7928,7 +7928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>13</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>26</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>51</v>
       </c>
@@ -7970,7 +7970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>11</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>36</v>
       </c>
@@ -7998,7 +7998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>27</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>8</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>34</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>29</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>15</v>
       </c>
@@ -8068,7 +8068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>32</v>
       </c>
@@ -8082,7 +8082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>37</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>24</v>
       </c>
@@ -8110,7 +8110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>20</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>27</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>8</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>34</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>29</v>
       </c>
@@ -8180,7 +8180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>15</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>49</v>
       </c>
@@ -8208,7 +8208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>13</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>51</v>
       </c>
@@ -8236,7 +8236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>11</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>48</v>
       </c>
@@ -8264,7 +8264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>33</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>26</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>32</v>
       </c>
@@ -8306,7 +8306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>37</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>57</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>23</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>37</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>24</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>27</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>34</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>29</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>49</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>13</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>26</v>
       </c>
@@ -8460,7 +8460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>11</v>
       </c>
@@ -8474,7 +8474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>36</v>
       </c>
@@ -8488,7 +8488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>32</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>48</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>40</v>
       </c>
@@ -8530,7 +8530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>39</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>22</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>53</v>
       </c>
@@ -8572,7 +8572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>48</v>
       </c>
@@ -8586,7 +8586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>9</v>
       </c>
@@ -8600,7 +8600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>41</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>35</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>52</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>47</v>
       </c>
@@ -8656,7 +8656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>44</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>43</v>
       </c>
@@ -8684,7 +8684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>19</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>57</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>56</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>54</v>
       </c>
@@ -8740,7 +8740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>45</v>
       </c>
@@ -8754,7 +8754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>17</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>47</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>56</v>
       </c>
@@ -8796,7 +8796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>53</v>
       </c>
@@ -8810,7 +8810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>41</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>30</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>52</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>48</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>44</v>
       </c>
@@ -8880,7 +8880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>19</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>57</v>
       </c>
@@ -8908,7 +8908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>17</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>39</v>
       </c>
@@ -8936,7 +8936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>54</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>16</v>
       </c>
@@ -8964,7 +8964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>6</v>
       </c>
@@ -8978,7 +8978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>30</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>41</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>35</v>
       </c>
@@ -9020,7 +9020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>40</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>48</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>12</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>32</v>
       </c>
@@ -9076,7 +9076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>42</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>25</v>
       </c>
@@ -9104,7 +9104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>53</v>
       </c>
@@ -9118,7 +9118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>54</v>
       </c>
@@ -9132,7 +9132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>39</v>
       </c>
@@ -9146,7 +9146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>17</v>
       </c>
@@ -9160,7 +9160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>16</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>53</v>
       </c>
@@ -9188,7 +9188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>9</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>41</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>35</v>
       </c>
@@ -9230,7 +9230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>52</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>30</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>6</v>
       </c>
@@ -9272,7 +9272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>48</v>
       </c>
@@ -9286,7 +9286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>32</v>
       </c>
@@ -9300,7 +9300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>44</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>54</v>
       </c>
@@ -9328,7 +9328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>56</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>39</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>47</v>
       </c>
@@ -9370,7 +9370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>32</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>44</v>
       </c>
@@ -9398,7 +9398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>16</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>30</v>
       </c>
@@ -9426,7 +9426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>41</v>
       </c>
@@ -9440,7 +9440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>53</v>
       </c>
@@ -9454,7 +9454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>9</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>52</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>6</v>
       </c>
@@ -9496,7 +9496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>48</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>14</v>
       </c>
@@ -9524,7 +9524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>47</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>12</v>
       </c>
@@ -9552,7 +9552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>39</v>
       </c>
@@ -9566,7 +9566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>54</v>
       </c>
@@ -9580,7 +9580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>17</v>
       </c>
@@ -9594,7 +9594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>53</v>
       </c>
@@ -9608,7 +9608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>9</v>
       </c>
@@ -9622,7 +9622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>35</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>52</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>6</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>48</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>14</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>32</v>
       </c>
@@ -9706,7 +9706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>44</v>
       </c>
@@ -9720,7 +9720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>16</v>
       </c>
@@ -9734,7 +9734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>25</v>
       </c>
@@ -9748,7 +9748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>43</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>56</v>
       </c>
@@ -9776,7 +9776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>17</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>41</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>32</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>44</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>16</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>30</v>
       </c>
@@ -9860,7 +9860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>35</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>53</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>41</v>
       </c>
@@ -9902,7 +9902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>48</v>
       </c>
@@ -9916,7 +9916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>52</v>
       </c>
@@ -9930,7 +9930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>6</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>12</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>43</v>
       </c>
@@ -9972,7 +9972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>54</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>19</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>56</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>17</v>
       </c>
@@ -10028,7 +10028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>53</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>9</v>
       </c>
@@ -10056,7 +10056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>48</v>
       </c>
@@ -10070,7 +10070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>41</v>
       </c>
@@ -10084,7 +10084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>35</v>
       </c>
@@ -10098,7 +10098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>6</v>
       </c>
@@ -10112,7 +10112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>12</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>14</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>52</v>
       </c>
@@ -10154,7 +10154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>44</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>16</v>
       </c>
@@ -10182,7 +10182,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>47</v>
       </c>
@@ -10196,7 +10196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>54</v>
       </c>
@@ -10210,7 +10210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>56</v>
       </c>
@@ -10224,7 +10224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>17</v>
       </c>
@@ -10238,7 +10238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>14</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>25</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>44</v>
       </c>
@@ -10280,7 +10280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>16</v>
       </c>
@@ -10294,7 +10294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>35</v>
       </c>
@@ -10308,7 +10308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>53</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>41</v>
       </c>
@@ -10336,7 +10336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>48</v>
       </c>
@@ -10350,7 +10350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>52</v>
       </c>
@@ -10364,7 +10364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>6</v>
       </c>
@@ -10378,7 +10378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>12</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>32</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>43</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>19</v>
       </c>
@@ -10434,7 +10434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>9</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>54</v>
       </c>
@@ -10462,7 +10462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>56</v>
       </c>
@@ -10476,7 +10476,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>25</v>
       </c>
@@ -10490,7 +10490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>44</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>16</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>41</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>35</v>
       </c>
@@ -10546,7 +10546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>53</v>
       </c>
@@ -10560,7 +10560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>56</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>48</v>
       </c>
@@ -10588,7 +10588,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>6</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>12</v>
       </c>
@@ -10616,7 +10616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>14</v>
       </c>
@@ -10630,7 +10630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>54</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>19</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>30</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>39</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>17</v>
       </c>
@@ -10700,7 +10700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>47</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>32</v>
       </c>
@@ -10728,7 +10728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>25</v>
       </c>
@@ -10742,7 +10742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>44</v>
       </c>
@@ -10756,7 +10756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>41</v>
       </c>
@@ -10770,7 +10770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>53</v>
       </c>
@@ -10784,7 +10784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>48</v>
       </c>
@@ -10798,7 +10798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>9</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>52</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>6</v>
       </c>
@@ -10840,7 +10840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>30</v>
       </c>
@@ -10854,7 +10854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>10</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>54</v>
       </c>
@@ -10882,7 +10882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>56</v>
       </c>
@@ -10896,7 +10896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>53</v>
       </c>
@@ -10910,7 +10910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>9</v>
       </c>
@@ -10924,7 +10924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>41</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>52</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>6</v>
       </c>
@@ -10966,7 +10966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>12</v>
       </c>
@@ -10980,7 +10980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>14</v>
       </c>
@@ -10994,7 +10994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>32</v>
       </c>
@@ -11008,7 +11008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>44</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>16</v>
       </c>
@@ -11036,7 +11036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>54</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>47</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>30</v>
       </c>
@@ -11078,7 +11078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>56</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>39</v>
       </c>
@@ -11106,7 +11106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>17</v>
       </c>
@@ -11120,7 +11120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>14</v>
       </c>
@@ -11134,7 +11134,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>43</v>
       </c>
@@ -11148,7 +11148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>44</v>
       </c>
@@ -11162,7 +11162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>16</v>
       </c>
@@ -11176,7 +11176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>41</v>
       </c>
@@ -11190,7 +11190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>53</v>
       </c>
@@ -11204,7 +11204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>9</v>
       </c>
@@ -11218,7 +11218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>30</v>
       </c>
@@ -11232,7 +11232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>54</v>
       </c>
@@ -11246,7 +11246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>6</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>12</v>
       </c>
@@ -11274,7 +11274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>22</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>56</v>
       </c>
@@ -11302,7 +11302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>39</v>
       </c>
@@ -11316,7 +11316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>17</v>
       </c>
@@ -11330,7 +11330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>53</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>9</v>
       </c>
@@ -11358,7 +11358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>41</v>
       </c>
@@ -11372,7 +11372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>35</v>
       </c>
@@ -11386,7 +11386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>52</v>
       </c>
@@ -11400,7 +11400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>6</v>
       </c>
@@ -11414,7 +11414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>12</v>
       </c>
@@ -11428,7 +11428,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>10</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>32</v>
       </c>
@@ -11456,7 +11456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>44</v>
       </c>
@@ -11470,7 +11470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>16</v>
       </c>
@@ -11484,7 +11484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>25</v>
       </c>
@@ -11498,7 +11498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>28</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>47</v>
       </c>
@@ -11526,7 +11526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>22</v>
       </c>
@@ -11540,7 +11540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>56</v>
       </c>
@@ -11554,7 +11554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>54</v>
       </c>
@@ -11568,7 +11568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>43</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>12</v>
       </c>
@@ -11596,7 +11596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>43</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>25</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>44</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>16</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>47</v>
       </c>
@@ -11666,7 +11666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>22</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>48</v>
       </c>
@@ -11694,7 +11694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>41</v>
       </c>
@@ -11708,7 +11708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>35</v>
       </c>
@@ -11722,7 +11722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>52</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>30</v>
       </c>
@@ -11750,7 +11750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>19</v>
       </c>
@@ -11764,7 +11764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>28</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>39</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>54</v>
       </c>
@@ -11806,7 +11806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>17</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>39</v>
       </c>
@@ -11834,7 +11834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>14</v>
       </c>
@@ -11848,7 +11848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>16</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>44</v>
       </c>
@@ -11876,7 +11876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>32</v>
       </c>
@@ -11890,7 +11890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>49</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>40</v>
       </c>
@@ -11918,7 +11918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="723" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>48</v>
       </c>
@@ -11932,7 +11932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="724" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>9</v>
       </c>
@@ -11946,7 +11946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>6</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="726" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>50</v>
       </c>
@@ -11974,7 +11974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="727" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>47</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="728" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>30</v>
       </c>
@@ -12002,7 +12002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="729" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>38</v>
       </c>
@@ -12016,7 +12016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="730" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>12</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="731" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>40</v>
       </c>
@@ -12044,7 +12044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="732" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>57</v>
       </c>
@@ -12058,7 +12058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="733" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>19</v>
       </c>
@@ -12072,7 +12072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="734" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>17</v>
       </c>
@@ -12086,7 +12086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="735" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>53</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>48</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="737" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>9</v>
       </c>
@@ -12128,7 +12128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>46</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>52</v>
       </c>
@@ -12156,7 +12156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>6</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>39</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>14</v>
       </c>
@@ -12198,7 +12198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>30</v>
       </c>
@@ -12212,7 +12212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>38</v>
       </c>
@@ -12226,7 +12226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>12</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>14</v>
       </c>
@@ -12254,7 +12254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>40</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>57</v>
       </c>
@@ -12282,7 +12282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="749" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>17</v>
       </c>
@@ -12296,7 +12296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="750" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>53</v>
       </c>
@@ -12310,7 +12310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="751" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>48</v>
       </c>
@@ -12324,7 +12324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="752" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>41</v>
       </c>
@@ -12338,7 +12338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>46</v>
       </c>
@@ -12352,7 +12352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>54</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="755" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>6</v>
       </c>
@@ -12380,7 +12380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="756" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>39</v>
       </c>
@@ -12394,7 +12394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="757" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>47</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="758" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>53</v>
       </c>
@@ -12422,7 +12422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="759" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>22</v>
       </c>
@@ -12436,7 +12436,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="760" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>48</v>
       </c>
@@ -12450,7 +12450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="761" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>52</v>
       </c>
@@ -12464,7 +12464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="762" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>46</v>
       </c>
@@ -12478,7 +12478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="763" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>12</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="764" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>14</v>
       </c>
@@ -12506,7 +12506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="765" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>32</v>
       </c>
@@ -12520,7 +12520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="766" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>40</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="767" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>57</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="768" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>35</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="769" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>47</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="770" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>43</v>
       </c>
@@ -12590,7 +12590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="771" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>39</v>
       </c>
@@ -12604,7 +12604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="772" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>54</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="773" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>10</v>
       </c>
@@ -12632,7 +12632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="774" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>44</v>
       </c>
@@ -12646,7 +12646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="775" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>53</v>
       </c>
@@ -12660,7 +12660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="776" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>9</v>
       </c>
@@ -12674,7 +12674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="777" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>41</v>
       </c>
@@ -12688,7 +12688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="778" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>52</v>
       </c>
@@ -12702,7 +12702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="779" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>46</v>
       </c>
@@ -12716,7 +12716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="780" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>6</v>
       </c>
@@ -12730,7 +12730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="781" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>14</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="782" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>40</v>
       </c>
@@ -12758,7 +12758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="783" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>57</v>
       </c>
@@ -12772,7 +12772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="784" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>35</v>
       </c>
@@ -12786,7 +12786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="785" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>44</v>
       </c>
@@ -12800,7 +12800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="786" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>47</v>
       </c>
@@ -12814,7 +12814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="787" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>48</v>
       </c>
@@ -12828,7 +12828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="788" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>30</v>
       </c>
@@ -12842,7 +12842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="789" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>54</v>
       </c>
@@ -12856,7 +12856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="790" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>17</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="791" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>40</v>
       </c>
@@ -12884,7 +12884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="792" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>57</v>
       </c>
@@ -12898,7 +12898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="793" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>15</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="794" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>35</v>
       </c>
@@ -12926,7 +12926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="795" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>44</v>
       </c>
@@ -12940,7 +12940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="796" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>53</v>
       </c>
@@ -12954,7 +12954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="797" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>41</v>
       </c>
@@ -12968,7 +12968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="798" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>52</v>
       </c>
@@ -12982,7 +12982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="799" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>46</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="800" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>12</v>
       </c>
@@ -13010,7 +13010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="801" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>42</v>
       </c>
@@ -13024,7 +13024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="802" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>56</v>
       </c>
@@ -13038,7 +13038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="803" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>48</v>
       </c>
@@ -13052,7 +13052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="804" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>54</v>
       </c>
@@ -13066,7 +13066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="805" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>17</v>
       </c>
@@ -13080,7 +13080,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="806" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>53</v>
       </c>
@@ -13094,7 +13094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="807" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>41</v>
       </c>
@@ -13108,7 +13108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="808" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>48</v>
       </c>
@@ -13122,7 +13122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="809" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>54</v>
       </c>
@@ -13136,7 +13136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="810" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>52</v>
       </c>
@@ -13150,7 +13150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="811" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>46</v>
       </c>
@@ -13164,7 +13164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="812" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>9</v>
       </c>
@@ -13178,7 +13178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="813" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>44</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="814" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>40</v>
       </c>
@@ -13206,7 +13206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="815" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>57</v>
       </c>
@@ -13220,7 +13220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="816" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>17</v>
       </c>
@@ -13234,7 +13234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="817" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>47</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="818" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>56</v>
       </c>
@@ -13262,7 +13262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="819" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>22</v>
       </c>
@@ -13276,7 +13276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="820" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>7</v>
       </c>
@@ -13290,7 +13290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="821" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>40</v>
       </c>
@@ -13304,7 +13304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="822" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>44</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="823" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>57</v>
       </c>
@@ -13332,7 +13332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="824" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>35</v>
       </c>
@@ -13346,7 +13346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="825" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>29</v>
       </c>
@@ -13360,7 +13360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="826" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>53</v>
       </c>
@@ -13374,7 +13374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="827" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>41</v>
       </c>
@@ -13388,7 +13388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="828" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>26</v>
       </c>
@@ -13402,7 +13402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="829" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>52</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="830" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>46</v>
       </c>
@@ -13430,7 +13430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="831" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>48</v>
       </c>
@@ -13444,7 +13444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="832" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>56</v>
       </c>
@@ -13458,7 +13458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="833" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>22</v>
       </c>
@@ -13472,7 +13472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="834" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>47</v>
       </c>
@@ -13486,7 +13486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="835" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>54</v>
       </c>
@@ -13500,7 +13500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="836" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>53</v>
       </c>
@@ -13514,7 +13514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="837" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>41</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="838" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>9</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="839" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>54</v>
       </c>
@@ -13556,7 +13556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="840" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>6</v>
       </c>
@@ -13570,7 +13570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="841" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>22</v>
       </c>
@@ -13584,7 +13584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="842" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>48</v>
       </c>
@@ -13598,7 +13598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="843" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>31</v>
       </c>
@@ -13612,7 +13612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="844" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>35</v>
       </c>
@@ -13626,7 +13626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="845" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>44</v>
       </c>
@@ -13640,7 +13640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="846" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>25</v>
       </c>
@@ -13654,7 +13654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="847" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>7</v>
       </c>
@@ -13668,7 +13668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="848" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>56</v>
       </c>
@@ -13682,7 +13682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="849" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>30</v>
       </c>
@@ -13696,7 +13696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="850" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>39</v>
       </c>
@@ -13710,7 +13710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="851" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>21</v>
       </c>
@@ -13724,7 +13724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="852" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>28</v>
       </c>
@@ -13738,7 +13738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="853" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>53</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="854" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>56</v>
       </c>
@@ -13766,7 +13766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="855" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>48</v>
       </c>
@@ -13780,7 +13780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="856" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>54</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="857" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>6</v>
       </c>
@@ -13808,7 +13808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="858" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>12</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="859" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>14</v>
       </c>
@@ -13836,7 +13836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="860" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>40</v>
       </c>
@@ -13850,7 +13850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="861" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>35</v>
       </c>
@@ -13864,7 +13864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="862" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>44</v>
       </c>
@@ -13878,7 +13878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="863" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>10</v>
       </c>
@@ -13892,7 +13892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="864" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>39</v>
       </c>
@@ -13906,7 +13906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="865" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>47</v>
       </c>
@@ -13920,7 +13920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="866" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>18</v>
       </c>
@@ -13934,7 +13934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="867" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>28</v>
       </c>
@@ -13948,7 +13948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="868" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>47</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="869" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>56</v>
       </c>
@@ -13976,7 +13976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="870" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>41</v>
       </c>
@@ -13990,7 +13990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="871" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>35</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="872" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>28</v>
       </c>
@@ -14018,7 +14018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="873" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>6</v>
       </c>
@@ -14032,7 +14032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="874" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>12</v>
       </c>
@@ -14046,7 +14046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="875" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>46</v>
       </c>
@@ -14060,7 +14060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="876" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>48</v>
       </c>
@@ -14074,7 +14074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="877" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>43</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="878" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>25</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="879" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>39</v>
       </c>
@@ -14116,7 +14116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="880" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>30</v>
       </c>
@@ -14130,7 +14130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="881" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>33</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="882" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>17</v>
       </c>
@@ -14158,7 +14158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="883" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>46</v>
       </c>
@@ -14172,7 +14172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="884" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>48</v>
       </c>
@@ -14186,7 +14186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="885" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>40</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="886" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>54</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="887" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>17</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="888" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>47</v>
       </c>
@@ -14242,7 +14242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="889" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>9</v>
       </c>
@@ -14256,7 +14256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="890" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>41</v>
       </c>
@@ -14270,7 +14270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="891" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>52</v>
       </c>
@@ -14284,7 +14284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="892" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>6</v>
       </c>
@@ -14298,7 +14298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="893" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>12</v>
       </c>
@@ -14312,7 +14312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="894" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>39</v>
       </c>
@@ -14326,7 +14326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="895" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>56</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="896" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>22</v>
       </c>
